--- a/hw2fintools/xlsx/schema.xlsx
+++ b/hw2fintools/xlsx/schema.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harveywargo/Desktop/GithubProjects/hw2fintools/hw2fintools/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D4C2FA-F035-8745-B9FA-4FA72CF151E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6875E5-CFD3-CC41-B721-FEB475D9638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3020" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{70A1AB90-009B-1840-B6A9-D87D55CDB664}"/>
+    <workbookView xWindow="3020" yWindow="760" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{70A1AB90-009B-1840-B6A9-D87D55CDB664}"/>
   </bookViews>
   <sheets>
     <sheet name="schema1-v1" sheetId="1" r:id="rId1"/>
     <sheet name="schema2-v1" sheetId="2" r:id="rId2"/>
+    <sheet name="schema3-v1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>Key</t>
   </si>
@@ -79,6 +80,15 @@
   </si>
   <si>
     <t>PricePerShare</t>
+  </si>
+  <si>
+    <t>DivPayDeclared</t>
+  </si>
+  <si>
+    <t>FwdDiv</t>
+  </si>
+  <si>
+    <t>FwdDivYield</t>
   </si>
 </sst>
 </file>
@@ -134,7 +144,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -189,7 +219,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8F805C0-7D92-8542-8CB3-51CB0A4D1696}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8F805C0-7D92-8542-8CB3-51CB0A4D1696}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:D9" xr:uid="{E8F805C0-7D92-8542-8CB3-51CB0A4D1696}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{CA32C398-127D-0D4B-9EBE-0C2637D66E4A}" name="Key"/>
@@ -202,13 +232,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD0D5D0C-8D25-BE44-AAC8-1333689405B6}" name="Table2" displayName="Table2" ref="A1:D3" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD0D5D0C-8D25-BE44-AAC8-1333689405B6}" name="Table2" displayName="Table2" ref="A1:D3" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:D3" xr:uid="{BD0D5D0C-8D25-BE44-AAC8-1333689405B6}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4ED3BDA3-1471-9E47-8C28-386684923C21}" name="Key"/>
     <tableColumn id="2" xr3:uid="{200C54BD-AABA-004A-BC8B-2EEB801CDEEC}" name="Value"/>
     <tableColumn id="3" xr3:uid="{DAA7BAD4-2901-284B-8441-6F0902552B9A}" name="ValueType"/>
     <tableColumn id="4" xr3:uid="{9DA146F4-6909-424E-80FE-3C1D79EF1D12}" name="Required"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{264A1E7F-85E9-2747-9793-CD47967BC788}" name="Table24" displayName="Table24" ref="A1:D10" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:D10" xr:uid="{264A1E7F-85E9-2747-9793-CD47967BC788}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D3">
+    <sortCondition ref="A1:A3"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D72FBAA3-570B-B741-8FDD-EF6B8F9855E9}" name="Key"/>
+    <tableColumn id="2" xr3:uid="{963ECBD3-DED8-E540-9F2B-C83EFECFEFC9}" name="Value"/>
+    <tableColumn id="3" xr3:uid="{2F2754C1-3522-904E-AA0C-A0464B117033}" name="ValueType"/>
+    <tableColumn id="4" xr3:uid="{8C0EEEEA-293C-D44C-96C9-D6EF4012F99C}" name="Required"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -657,4 +703,87 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D195E6D7-01A9-0C4F-A3F5-E821AE70124F}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/hw2fintools/xlsx/schema.xlsx
+++ b/hw2fintools/xlsx/schema.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harveywargo/Desktop/GithubProjects/hw2fintools/hw2fintools/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6875E5-CFD3-CC41-B721-FEB475D9638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC3324B-A444-5747-9A57-01113A0BEAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3020" yWindow="760" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{70A1AB90-009B-1840-B6A9-D87D55CDB664}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="3" xr2:uid="{70A1AB90-009B-1840-B6A9-D87D55CDB664}"/>
   </bookViews>
   <sheets>
     <sheet name="schema1-v1" sheetId="1" r:id="rId1"/>
     <sheet name="schema2-v1" sheetId="2" r:id="rId2"/>
     <sheet name="schema3-v1" sheetId="3" r:id="rId3"/>
+    <sheet name="schema4-v1" sheetId="4" r:id="rId4"/>
+    <sheet name="schema5-v1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
   <si>
     <t>Key</t>
   </si>
@@ -89,6 +91,33 @@
   </si>
   <si>
     <t>FwdDivYield</t>
+  </si>
+  <si>
+    <t>SharePriceMin</t>
+  </si>
+  <si>
+    <t>SharePriceMean</t>
+  </si>
+  <si>
+    <t>SharePriceMax</t>
+  </si>
+  <si>
+    <t>SharePriceMedian</t>
+  </si>
+  <si>
+    <t>DivYieldMin</t>
+  </si>
+  <si>
+    <t>DivYieldMax</t>
+  </si>
+  <si>
+    <t>DivYieldMedian</t>
+  </si>
+  <si>
+    <t>DateCy</t>
+  </si>
+  <si>
+    <t>DivPaidTotal</t>
   </si>
 </sst>
 </file>
@@ -111,7 +140,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -121,6 +150,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -137,14 +172,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -219,7 +275,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8F805C0-7D92-8542-8CB3-51CB0A4D1696}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8F805C0-7D92-8542-8CB3-51CB0A4D1696}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:D9" xr:uid="{E8F805C0-7D92-8542-8CB3-51CB0A4D1696}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{CA32C398-127D-0D4B-9EBE-0C2637D66E4A}" name="Key"/>
@@ -232,7 +288,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD0D5D0C-8D25-BE44-AAC8-1333689405B6}" name="Table2" displayName="Table2" ref="A1:D3" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD0D5D0C-8D25-BE44-AAC8-1333689405B6}" name="Table2" displayName="Table2" ref="A1:D3" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:D3" xr:uid="{BD0D5D0C-8D25-BE44-AAC8-1333689405B6}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4ED3BDA3-1471-9E47-8C28-386684923C21}" name="Key"/>
@@ -245,7 +301,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{264A1E7F-85E9-2747-9793-CD47967BC788}" name="Table24" displayName="Table24" ref="A1:D10" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{264A1E7F-85E9-2747-9793-CD47967BC788}" name="Table24" displayName="Table24" ref="A1:D10" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:D10" xr:uid="{264A1E7F-85E9-2747-9793-CD47967BC788}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D3">
     <sortCondition ref="A1:A3"/>
@@ -255,6 +311,19 @@
     <tableColumn id="2" xr3:uid="{963ECBD3-DED8-E540-9F2B-C83EFECFEFC9}" name="Value"/>
     <tableColumn id="3" xr3:uid="{2F2754C1-3522-904E-AA0C-A0464B117033}" name="ValueType"/>
     <tableColumn id="4" xr3:uid="{8C0EEEEA-293C-D44C-96C9-D6EF4012F99C}" name="Required"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6863BC80-DBDC-4B4E-A5E1-9DB8B2AF715A}" name="Table4" displayName="Table4" ref="A1:D11" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:D11" xr:uid="{6863BC80-DBDC-4B4E-A5E1-9DB8B2AF715A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{52815CE5-55E8-8C45-8A6A-73478F1F2D41}" name="Key"/>
+    <tableColumn id="2" xr3:uid="{F4A3991E-D47A-AB4D-9EA0-FCECE44B96C5}" name="Value"/>
+    <tableColumn id="3" xr3:uid="{36BC6DEA-682F-FF44-881D-94FB76D2585E}" name="ValueType"/>
+    <tableColumn id="4" xr3:uid="{07334AA2-0B56-FA4D-9804-31D10889DAD4}" name="Required"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -786,4 +855,122 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5198A87F-A707-6740-AD9B-CE92EF5213F3}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D15AB6-317D-1A4F-96EC-D856163CBEA6}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>